--- a/practica_final/opcion_B_esports/datos_limpios/Datos_completo.xlsx
+++ b/practica_final/opcion_B_esports/datos_limpios/Datos_completo.xlsx
@@ -25304,7 +25304,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-s1</t>
+          <t>Primera</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -25487,7 +25487,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2025-s1</t>
+          <t>Primera</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -25742,7 +25742,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2025-s1</t>
+          <t>Primera</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -25920,7 +25920,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2025-s1</t>
+          <t>Primera</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -25972,7 +25972,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2025-s1</t>
+          <t>Primera</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -25992,7 +25992,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2025-s1</t>
+          <t>Primera</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -26018,7 +26018,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2025-s1</t>
+          <t>Primera</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2025-s1</t>
+          <t>Primera</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -26233,7 +26233,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2025-s1</t>
+          <t>Primera</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -26646,7 +26646,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2025-s1</t>
+          <t>Primera</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -26987,7 +26987,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2025-s1</t>
+          <t>Primera</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -27205,7 +27205,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2025-s1</t>
+          <t>Primera</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -27225,7 +27225,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2025-s1</t>
+          <t>Primera</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -27368,7 +27368,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2025-s1</t>
+          <t>Primera</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -27563,7 +27563,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2025-s1</t>
+          <t>Primera</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -28088,7 +28088,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2025-s1</t>
+          <t>Primera</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2025-s1</t>
+          <t>Primera</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
